--- a/WorkBot/main/data/order_archive/Performance Food/Performance Food_Easthill_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Performance Food/Performance Food_Easthill_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,48 +794,6 @@
         <v>102.37</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TN374</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Natalie's - Lemonade</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="E21" t="n">
-        <v>10.39</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AH252</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Natalie's - Orange Juice</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
